--- a/artfynd/A 62846-2023 artfynd.xlsx
+++ b/artfynd/A 62846-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62846-2023 artfynd.xlsx
+++ b/artfynd/A 62846-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110212447</v>
+        <v>110212417</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>324390.5710141304</v>
+        <v>324355</v>
       </c>
       <c r="R2" t="n">
-        <v>6449909.066476046</v>
+        <v>6450156</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110212585</v>
+        <v>110212447</v>
       </c>
       <c r="B3" t="n">
-        <v>57587</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,61 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100141</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Högen, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>324378.2485861456</v>
+        <v>324391</v>
       </c>
       <c r="R3" t="n">
-        <v>6449834.048842314</v>
+        <v>6449909</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:49</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:49</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +871,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -924,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110212439</v>
+        <v>110212436</v>
       </c>
       <c r="B4" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -964,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>324348.1095455033</v>
+        <v>324292</v>
       </c>
       <c r="R4" t="n">
-        <v>6450085.847366761</v>
+        <v>6449997</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -994,22 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:09</t>
+          <t>06:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:09</t>
+          <t>06:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110212584</v>
+        <v>110212437</v>
       </c>
       <c r="B5" t="n">
-        <v>57587</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,61 +1007,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100141</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Högen, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>324380.3387292902</v>
+        <v>324312</v>
       </c>
       <c r="R5" t="n">
-        <v>6449833.427848491</v>
+        <v>6450097</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1130,22 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,15 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110212437</v>
+        <v>110212439</v>
       </c>
       <c r="B6" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>324312.0979530362</v>
+        <v>324348</v>
       </c>
       <c r="R6" t="n">
-        <v>6450097.482280889</v>
+        <v>6450085</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1242,22 +1168,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-04-14</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>06:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-04-14</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>06:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,15 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110212586</v>
+        <v>110212441</v>
       </c>
       <c r="B7" t="n">
-        <v>57587</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,61 +1221,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100141</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högen, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>324376.1350850029</v>
+        <v>324351</v>
       </c>
       <c r="R7" t="n">
-        <v>6449834.142451413</v>
+        <v>6450052</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1378,22 +1275,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>06:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>06:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,37 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110212438</v>
+        <v>110212415</v>
       </c>
       <c r="B8" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1460,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>324294.1427156732</v>
+        <v>324321</v>
       </c>
       <c r="R8" t="n">
-        <v>6450170.137883436</v>
+        <v>6449791</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1490,22 +1382,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-04-14</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>04:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-04-14</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>04:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1532,15 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110212445</v>
+        <v>110212583</v>
       </c>
       <c r="B9" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,37 +1435,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>100141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Högen, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>324386.0259440427</v>
+        <v>324379</v>
       </c>
       <c r="R9" t="n">
-        <v>6449914.023464403</v>
+        <v>6449833</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1602,22 +1503,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,15 +1545,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110212417</v>
+        <v>110212584</v>
       </c>
       <c r="B10" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,37 +1556,61 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>100141</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Högen, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>324355.4901776543</v>
+        <v>324380</v>
       </c>
       <c r="R10" t="n">
-        <v>6450156.852067532</v>
+        <v>6449833</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1714,22 +1634,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>06:24</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>06:24</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1756,15 +1676,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110212443</v>
+        <v>110212585</v>
       </c>
       <c r="B11" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,37 +1687,61 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>100141</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Högen, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>324364.2386303181</v>
+        <v>324378</v>
       </c>
       <c r="R11" t="n">
-        <v>6449995.834378229</v>
+        <v>6449834</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1826,22 +1765,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,6 +1789,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1868,15 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110212419</v>
+        <v>110212586</v>
       </c>
       <c r="B12" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,37 +1819,61 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100141</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Högen, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>324313.8477470257</v>
+        <v>324377</v>
       </c>
       <c r="R12" t="n">
-        <v>6450041.395385897</v>
+        <v>6449834</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1938,22 +1897,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>05:36</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>05:36</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1980,15 +1939,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110212441</v>
+        <v>110212427</v>
       </c>
       <c r="B13" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1996,21 +1950,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2020,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>324351.4161577828</v>
+        <v>324352</v>
       </c>
       <c r="R13" t="n">
-        <v>6450052.940718519</v>
+        <v>6450010</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2050,22 +2004,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>06:04</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>06:04</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2092,15 +2046,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110212427</v>
+        <v>110212445</v>
       </c>
       <c r="B14" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,10 +2081,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>324352.1421959085</v>
+        <v>324386</v>
       </c>
       <c r="R14" t="n">
-        <v>6450009.58019027</v>
+        <v>6449914</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2162,22 +2111,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2204,15 +2153,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110212583</v>
+        <v>110212428</v>
       </c>
       <c r="B15" t="n">
-        <v>57587</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2220,51 +2164,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100141</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>äggklumpar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>ägg</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Högen, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>324378.2018695236</v>
+        <v>324341</v>
       </c>
       <c r="R15" t="n">
-        <v>6449832.994070559</v>
+        <v>6449993</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2288,22 +2218,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2327,6 +2257,327 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>110212443</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Högen, Boh</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>324364</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6449996</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Andreas Källman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Andreas Källman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>110212419</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Högen, Boh</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>324313</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6450041</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>05:36</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>05:36</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Andreas Källman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Andreas Källman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>110212438</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Högen, Boh</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>324295</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6450170</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-04-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-04-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Andreas Källman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Andreas Källman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62846-2023 artfynd.xlsx
+++ b/artfynd/A 62846-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212417</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212447</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212436</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212437</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212439</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212441</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212415</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1542,6 +1582,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212583</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1673,6 +1718,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212584</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1805,6 +1855,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212585</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1936,6 +1991,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212586</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2043,6 +2103,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212427</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2150,6 +2215,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212445</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2257,6 +2327,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212428</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2364,6 +2439,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212443</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2471,6 +2551,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212419</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2578,8 +2663,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212438</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>